--- a/build/report-suite/chris-update-2026-07-29/ChangeList-2026-07-29.xlsx
+++ b/build/report-suite/chris-update-2026-07-29/ChangeList-2026-07-29.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Change list" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Push queue" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Wave 2 - WIP identifier" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2248,7 +2249,6 @@
           <t>(new, no C-ID yet)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2291,6 +2291,196 @@
       <c r="D28" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/30418</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="110" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Wave 2 (2026-07-29, later): Chris answered the WIP-identifier question - 'A is the correct answer' = Work In Progress ALSO uses VIN, falling back to Unit #, then plate (verbatim + standing notes: wip-identifier-answer-2026-07-29.md). APPLIED-LOCALLY, awaiting push authorization. Rule-28 mini-audit: USEFUL 4/4 KEEP; MAKES SENSE 4/4 SENSIBLE; GENUINE + LAYMAN-RUNNABLE 4/4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Op</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Internal ID</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>TestRail Case ID</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>TestRail link</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>What changed (plain)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>update_case</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>WIP-COL-05</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>C30470</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30470</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Asset cell identifier: serial number -&gt; VIN, falling back to Unit #, then plate; tester VIN-terminology note added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>update_case</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>WIP-FLT-03</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>C30500</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30500</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Asset filter options + type-ahead: serial -&gt; VIN chain; tester VIN-terminology note added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>update_case</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>WIP-SORT-03</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>C30485</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30485</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Asset sort key: serial number -&gt; the identifier shown (VIN chain).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>update_case</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>WIP-EXP-07</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>C30516</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30516</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Export-header caveat: on-screen Asset data now the VIN chain (was serial); caveat itself unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>(none - notes only)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>SBC-LBL-01</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>C30134</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30134</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Local notes-only: 'WIP question queued' residue closed (answered A). Notes are not a pushed TestRail field.</t>
         </is>
       </c>
     </row>
